--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487938_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487938_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8969</v>
+        <v>3.1993</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7308</v>
+        <v>2.9451</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1662</v>
+        <v>0.2542</v>
       </c>
       <c r="G2" t="n">
         <v>1.2625</v>
@@ -610,13 +610,13 @@
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.227</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5748</v>
+        <v>-0.3605</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3478</v>
+        <v>0.4358</v>
       </c>
       <c r="V2" t="n">
         <v>0.8208</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. VAN DER HEIJDEN</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9081</v>
+        <v>1.6473</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0011</v>
+        <v>0.8116</v>
       </c>
       <c r="F3" t="n">
-        <v>1.907</v>
+        <v>0.8356</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7533</v>
+        <v>0.2906</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5584</v>
+        <v>0.2816</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8051</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6763</v>
+        <v>0.8459</v>
       </c>
       <c r="K3" t="n">
-        <v>4.0975</v>
+        <v>0.7675</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5788</v>
+        <v>0.0784</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.923</v>
+        <v>-0.5553</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5391</v>
+        <v>-0.4859</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.3839</v>
+        <v>-0.0694</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.9137</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.2029</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2893</v>
+        <v>0.8325</v>
       </c>
       <c r="S3" t="n">
-        <v>1.77</v>
+        <v>0.5242</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5276999999999999</v>
+        <v>-0.0343</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2423</v>
+        <v>0.5585</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2984</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>1.2984</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>E. VAN DER HEIJDEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2862</v>
+        <v>0.7469</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5973000000000001</v>
+        <v>-0.749</v>
       </c>
       <c r="F4" t="n">
-        <v>0.6888</v>
+        <v>1.496</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2906</v>
+        <v>1.7533</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2816</v>
+        <v>3.5584</v>
       </c>
       <c r="I4" t="n">
-        <v>0.008999999999999999</v>
+        <v>-1.8051</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8459</v>
+        <v>4.6763</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7675</v>
+        <v>4.0975</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0784</v>
+        <v>0.5788</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5553</v>
+        <v>-2.923</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4859</v>
+        <v>-0.5391</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0694</v>
+        <v>-2.3839</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-5.2029</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8325</v>
+        <v>2.2893</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1631</v>
+        <v>0.6089</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2486</v>
+        <v>-0.2224</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4117</v>
+        <v>0.8312</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.2984</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.2984</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. HAYMAN</t>
+          <t>D. BULTO CASTILLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6329</v>
+        <v>0.5438</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0347</v>
+        <v>0.8238</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4019</v>
+        <v>-0.28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3724</v>
+        <v>0.2266</v>
       </c>
       <c r="H5" t="n">
-        <v>1.6844</v>
+        <v>1.1834</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.312</v>
+        <v>-0.9568</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1647</v>
+        <v>1.7086</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1255</v>
+        <v>1.6694</v>
       </c>
       <c r="L5" t="n">
         <v>0.0392</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7922</v>
+        <v>-1.482</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4411</v>
+        <v>-0.4859</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3512</v>
+        <v>-0.996</v>
       </c>
       <c r="P5" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1899</v>
+        <v>0.0467</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.1771</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2584</v>
+        <v>0.2238</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1782</v>
+        <v>-0.3538</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.0614</v>
+        <v>-0.7076</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1168</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. BULTO CASTILLO</t>
+          <t>D. HAYMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2121</v>
+        <v>0.2233</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6095</v>
+        <v>0.7133</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3974</v>
+        <v>-0.4899</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2266</v>
+        <v>0.3724</v>
       </c>
       <c r="H6" t="n">
-        <v>1.1834</v>
+        <v>1.6844</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.9568</v>
+        <v>-1.312</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7086</v>
+        <v>2.1647</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6694</v>
+        <v>2.1255</v>
       </c>
       <c r="L6" t="n">
         <v>0.0392</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.482</v>
+        <v>-1.7922</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4859</v>
+        <v>-0.4411</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.996</v>
+        <v>-1.3512</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2851</v>
+        <v>-0.2197</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3915</v>
+        <v>-0.39</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1064</v>
+        <v>0.1703</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3538</v>
+        <v>-1.1782</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.7076</v>
+        <v>-1.0614</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3538</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>M. AMADASUN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2713</v>
+        <v>-0.4032</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9866</v>
+        <v>1.6362</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2579</v>
+        <v>-2.0394</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3461</v>
+        <v>-1.2726</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7243</v>
+        <v>0.6778</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0704</v>
+        <v>-1.9504</v>
       </c>
       <c r="J7" t="n">
-        <v>2.5402</v>
+        <v>0.8135</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8348</v>
+        <v>0.7351</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7054</v>
+        <v>0.0784</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.8863</v>
+        <v>-2.0861</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1105</v>
+        <v>-0.0573</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.7758</v>
+        <v>-2.0288</v>
       </c>
       <c r="P7" t="n">
         <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.4568</v>
+        <v>-0.4162</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8731</v>
+        <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4723</v>
+        <v>-0.7144</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2643</v>
+        <v>-0.1586</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.208</v>
+        <v>-0.5558</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1309</v>
+        <v>1.1675</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1675</v>
+        <v>1.3975</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0366</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3708</v>
+        <v>-0.4768</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6422</v>
+        <v>1.9866</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.013</v>
+        <v>-2.4634</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2063</v>
+        <v>-0.3461</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3392</v>
+        <v>1.7243</v>
       </c>
       <c r="I8" t="n">
-        <v>1.8672</v>
+        <v>-2.0704</v>
       </c>
       <c r="J8" t="n">
-        <v>4.6394</v>
+        <v>2.5402</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4945</v>
+        <v>1.8348</v>
       </c>
       <c r="L8" t="n">
-        <v>4.145</v>
+        <v>0.7054</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4331</v>
+        <v>-2.8863</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1553</v>
+        <v>-0.1105</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.2778</v>
+        <v>-2.7758</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8325</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4974</v>
+        <v>-1.4568</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5904</v>
+        <v>-0.6778</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8539</v>
+        <v>-0.2643</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2635</v>
+        <v>-0.4136</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.3351</v>
+        <v>0.1309</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3538</v>
+        <v>1.1675</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.9813</v>
+        <v>-1.0366</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. AMADASUN</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0667</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2076</v>
+        <v>2.1064</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2743</v>
+        <v>-2.8075</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2726</v>
+        <v>2.2063</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6778</v>
+        <v>0.3392</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9504</v>
+        <v>1.8672</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8135</v>
+        <v>4.6394</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7351</v>
+        <v>0.4945</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0784</v>
+        <v>4.145</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0861</v>
+        <v>-2.4331</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0573</v>
+        <v>-0.1553</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.0288</v>
+        <v>-2.2778</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.4162</v>
+        <v>-2.4974</v>
       </c>
       <c r="R9" t="n">
-        <v>0.8325</v>
+        <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.3779</v>
+        <v>0.2601</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5872000000000001</v>
+        <v>0.3182</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7907</v>
+        <v>-0.058</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1675</v>
+        <v>-2.3351</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3975</v>
+        <v>-0.3538</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.23</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3201</v>
+        <v>-0.8137</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2802</v>
+        <v>0.2556</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0399</v>
+        <v>-1.0693</v>
       </c>
       <c r="G10" t="n">
         <v>-3.5187</v>
@@ -1234,13 +1234,13 @@
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8116</v>
+        <v>-0.3052</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6524</v>
+        <v>-0.1167</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1591</v>
+        <v>-0.1885</v>
       </c>
       <c r="V10" t="n">
         <v>2.8021</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5247</v>
+        <v>-2.466</v>
       </c>
       <c r="E11" t="n">
         <v>-2.71</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1853</v>
+        <v>0.244</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8619</v>
@@ -1312,13 +1312,13 @@
         <v>0.6244</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="T11" t="n">
         <v>-0.3138</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0672</v>
+        <v>0.1259</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2784</v>
+        <v>-3.3959</v>
       </c>
       <c r="E12" t="n">
         <v>-1.7628</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5156</v>
+        <v>-1.633</v>
       </c>
       <c r="G12" t="n">
         <v>-1.4173</v>
@@ -1390,13 +1390,13 @@
         <v>0.8325</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1931</v>
+        <v>-0.3105</v>
       </c>
       <c r="T12" t="n">
         <v>-0.06850000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1245</v>
+        <v>-0.242</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0437</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.8958</v>
+        <v>-1.8961</v>
       </c>
       <c r="E13" t="n">
-        <v>6.056799999999999</v>
+        <v>6.056800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.9527</v>
+        <v>-7.952700000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3049</v>
@@ -1459,7 +1459,7 @@
         <v>-18.1449</v>
       </c>
       <c r="P13" t="n">
-        <v>-9.999999999998899e-05</v>
+        <v>-0.000100000000000211</v>
       </c>
       <c r="Q13" t="n">
         <v>-14.5681</v>
@@ -1474,7 +1474,7 @@
         <v>-1.788</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8880000000000001</v>
+        <v>0.8876000000000004</v>
       </c>
       <c r="V13" t="n">
         <v>1.3089</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. ARBOSA ROLDAN</t>
+          <t>K. TORRES CUEVAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2241</v>
+        <v>3.6816</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2066</v>
+        <v>4.0552</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9825</v>
+        <v>-0.3736</v>
       </c>
       <c r="G14" t="n">
-        <v>3.4931</v>
+        <v>2.6494</v>
       </c>
       <c r="H14" t="n">
-        <v>2.1836</v>
+        <v>-4.433</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3095</v>
+        <v>7.0824</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6324</v>
+        <v>5.6666</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6819</v>
+        <v>-1.7342</v>
       </c>
       <c r="L14" t="n">
-        <v>1.9504</v>
+        <v>7.4008</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1393</v>
+        <v>-3.0172</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4984</v>
+        <v>-2.6988</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6409</v>
+        <v>-0.3184</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6244</v>
+        <v>-0.8325</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6649</v>
+        <v>2.2893</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8579</v>
+        <v>-0.1167</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3849</v>
+        <v>-0.4709</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4731</v>
+        <v>0.3543</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.7513</v>
+        <v>1.9813</v>
       </c>
       <c r="W14" t="n">
-        <v>0.23</v>
+        <v>1.9813</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.9813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>K. TORRES CUEVAS</t>
+          <t>H. ARBOSA ROLDAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1045</v>
+        <v>2.7265</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0907</v>
+        <v>3.8851</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9862</v>
+        <v>-1.1587</v>
       </c>
       <c r="G15" t="n">
-        <v>2.6494</v>
+        <v>3.4931</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.433</v>
+        <v>2.1836</v>
       </c>
       <c r="I15" t="n">
-        <v>7.0824</v>
+        <v>1.3095</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6666</v>
+        <v>4.6324</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.7342</v>
+        <v>2.6819</v>
       </c>
       <c r="L15" t="n">
-        <v>7.4008</v>
+        <v>1.9504</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.0172</v>
+        <v>-1.1393</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6988</v>
+        <v>-0.4984</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3184</v>
+        <v>-0.6409</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2893</v>
+        <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6937</v>
+        <v>0.3603</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4354</v>
+        <v>0.0634</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2583</v>
+        <v>0.2969</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9813</v>
+        <v>-1.7513</v>
       </c>
       <c r="W15" t="n">
-        <v>1.9813</v>
+        <v>0.23</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.9813</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. A NONGO BERTHOLD</t>
+          <t>C. JACOBS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.9291</v>
+        <v>2.6082</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3531</v>
+        <v>2.9927</v>
       </c>
       <c r="F16" t="n">
-        <v>0.576</v>
+        <v>-0.3844</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.6538</v>
+        <v>-0.0956</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.0939</v>
+        <v>-2.3734</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4401</v>
+        <v>2.2778</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2814</v>
+        <v>3.3706</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1639</v>
+        <v>-0.2951</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1176</v>
+        <v>3.6657</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9352</v>
+        <v>-3.4662</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2577</v>
+        <v>-2.0783</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3225</v>
+        <v>-1.3879</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0406</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R16" t="n">
-        <v>1.0406</v>
+        <v>2.0812</v>
       </c>
       <c r="S16" t="n">
-        <v>2.4185</v>
+        <v>0.3687</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4254</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.993</v>
+        <v>0.293</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1238</v>
+        <v>2.3351</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3538</v>
+        <v>1.6275</v>
       </c>
       <c r="X16" t="n">
-        <v>0.4776</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. JACOBS</t>
+          <t>M. DE PABLO DEL CASTILLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6066</v>
+        <v>1.4788</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4569</v>
+        <v>3.1059</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8502999999999999</v>
+        <v>-1.6271</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.0956</v>
+        <v>2.4621</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.3734</v>
+        <v>-1.0167</v>
       </c>
       <c r="I17" t="n">
-        <v>2.2778</v>
+        <v>3.4788</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3706</v>
+        <v>5.2058</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2951</v>
+        <v>0.8738</v>
       </c>
       <c r="L17" t="n">
-        <v>3.6657</v>
+        <v>4.3319</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.4662</v>
+        <v>-2.7437</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0783</v>
+        <v>-1.8905</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3879</v>
+        <v>-0.8532</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.2081</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.0812</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6329</v>
+        <v>-0.7138</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.46</v>
+        <v>-0.7086</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1729</v>
+        <v>-0.0052</v>
       </c>
       <c r="V17" t="n">
-        <v>2.3351</v>
+        <v>-0.4776</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6275</v>
+        <v>0.6899</v>
       </c>
       <c r="X17" t="n">
-        <v>0.7076</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. DE PABLO DEL CASTILLO</t>
+          <t>E. A NONGO BERTHOLD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2731</v>
+        <v>0.2219</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2486</v>
+        <v>0.1744</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9755</v>
+        <v>0.0475</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4621</v>
+        <v>-1.6538</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0167</v>
+        <v>-2.0939</v>
       </c>
       <c r="I18" t="n">
-        <v>3.4788</v>
+        <v>0.4401</v>
       </c>
       <c r="J18" t="n">
-        <v>5.2058</v>
+        <v>0.2814</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8738</v>
+        <v>0.1639</v>
       </c>
       <c r="L18" t="n">
-        <v>4.3319</v>
+        <v>0.1176</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.7437</v>
+        <v>-1.9352</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.8905</v>
+        <v>-2.2577</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8532</v>
+        <v>0.3225</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2081</v>
+        <v>1.0406</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2893</v>
+        <v>1.0406</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9194</v>
+        <v>0.7113</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.5658</v>
+        <v>0.2467</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3536</v>
+        <v>0.4645</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4776</v>
+        <v>0.1238</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6899</v>
+        <v>-0.3538</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.1675</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. PARDINA MOLINA</t>
+          <t>P. DIENE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2266</v>
+        <v>-0.6835</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2161</v>
+        <v>-0.9358</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4427</v>
+        <v>0.2523</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.674</v>
+        <v>-0.1133</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.1254</v>
+        <v>-0.9869</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5486</v>
+        <v>0.8736</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3267</v>
+        <v>1.4749</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8058999999999999</v>
+        <v>-0.6804</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4792</v>
+        <v>2.1554</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0007</v>
+        <v>-1.5883</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.9313</v>
+        <v>-0.3065</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0694</v>
+        <v>-1.2818</v>
       </c>
       <c r="P19" t="n">
-        <v>0.6244</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>1.8731</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4615</v>
+        <v>0.0979</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6831</v>
+        <v>-0.3295</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7784</v>
+        <v>0.4274</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1852</v>
+        <v>-0.4599</v>
       </c>
       <c r="W19" t="n">
-        <v>-1.1852</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. DIENE</t>
+          <t>J. PARDINA MOLINA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9358</v>
+        <v>-1.1805</v>
       </c>
       <c r="F20" t="n">
-        <v>0.403</v>
+        <v>0.2959</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1133</v>
+        <v>-1.674</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9869</v>
+        <v>-1.1254</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8736</v>
+        <v>-0.5486</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4749</v>
+        <v>0.3267</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6804</v>
+        <v>0.8058999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1554</v>
+        <v>-0.4792</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.5883</v>
+        <v>-2.0007</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3065</v>
+        <v>-1.9313</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2818</v>
+        <v>-0.0694</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2486</v>
+        <v>1.3503</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3295</v>
+        <v>0.7187</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.4599</v>
+        <v>-1.1852</v>
       </c>
       <c r="W20" t="n">
+        <v>-1.1852</v>
+      </c>
+      <c r="X20" t="n">
         <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>-0.4599</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0299</v>
+        <v>-1.8386</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.879</v>
+        <v>-0.7718</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1509</v>
+        <v>-1.0667</v>
       </c>
       <c r="G21" t="n">
         <v>-2.0155</v>
@@ -2092,13 +2092,13 @@
         <v>1.0406</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0144</v>
+        <v>0.1769</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.199</v>
+        <v>-0.0919</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1847</v>
+        <v>0.2688</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9055</v>
+        <v>-4.6999</v>
       </c>
       <c r="E22" t="n">
         <v>-3.3725</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.533</v>
+        <v>-1.3275</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7475000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>0.6244</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8259</v>
+        <v>-0.6204</v>
       </c>
       <c r="T22" t="n">
         <v>-0.3915</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4345</v>
+        <v>-0.229</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8751</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.8958</v>
+        <v>2.6104</v>
       </c>
       <c r="E23" t="n">
-        <v>7.952500000000001</v>
+        <v>7.952700000000002</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.056699999999999</v>
+        <v>-5.3423</v>
       </c>
       <c r="G23" t="n">
         <v>2.3049</v>
@@ -2248,19 +2248,19 @@
         <v>14.5683</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9001999999999998</v>
+        <v>1.6145</v>
       </c>
       <c r="T23" t="n">
         <v>-0.8877999999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>1.788</v>
+        <v>2.5023</v>
       </c>
       <c r="V23" t="n">
         <v>-1.3089</v>
       </c>
       <c r="W23" t="n">
-        <v>2.2821</v>
+        <v>2.282100000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-3.591</v>
